--- a/data/trans_orig/P1406-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1406-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de úlcera de estómago en 2012</t>
+          <t>Población con diagnóstico de úlcera de estómago en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>10129</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449401</t>
+          <t>449334</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>421441</t>
+          <t>421085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>875448</t>
+          <t>874247</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1847</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1847</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680640</t>
+          <t>680605</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>610255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1290894</t>
+          <t>1290887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10959</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13671</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>675599</t>
+          <t>675433</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698615</t>
+          <t>698430</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707618</t>
+          <t>707608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1377766</t>
+          <t>1378456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1388503</t>
+          <t>1388510</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25138</t>
+          <t>23878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18279</t>
+          <t>17112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>13900</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35096</t>
+          <t>34561</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589479</t>
+          <t>590739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>606168</t>
+          <t>606428</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>595985</t>
+          <t>597152</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610235</t>
+          <t>610176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1193784</t>
+          <t>1194319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1214696</t>
+          <t>1214980</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2070</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12814</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18414</t>
+          <t>18133</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9170</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>25482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>416615</t>
+          <t>417834</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427342</t>
+          <t>427359</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>429386</t>
+          <t>429667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442485</t>
+          <t>442470</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>850657</t>
+          <t>851747</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>868059</t>
+          <t>867761</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5218</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>18324</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>300216</t>
+          <t>300238</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>341348</t>
+          <t>341871</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>351901</t>
+          <t>352024</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>645758</t>
+          <t>645458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>658623</t>
+          <t>658564</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>19958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>19348</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32887</t>
+          <t>33585</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229093</t>
+          <t>229893</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243420</t>
+          <t>243569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>367698</t>
+          <t>368448</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382302</t>
+          <t>382288</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>604760</t>
+          <t>604062</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>623869</t>
+          <t>622607</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29268</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54677</t>
+          <t>54985</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31075</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57787</t>
+          <t>57239</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65841</t>
+          <t>67000</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>103391</t>
+          <t>104777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3372102</t>
+          <t>3371794</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3397511</t>
+          <t>3397097</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3496129</t>
+          <t>3496677</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3522841</t>
+          <t>3523205</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6877303</t>
+          <t>6875917</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6914853</t>
+          <t>6913694</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de úlcera de estómago en 2016</t>
+          <t>Población con diagnóstico de úlcera de estómago en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3710,82 +3710,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6977</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1992</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>7373</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>6974</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>388382</t>
+          <t>388778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>808229</t>
+          <t>808244</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>903</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7616</t>
+          <t>8403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583673</t>
+          <t>583631</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555928</t>
+          <t>555141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562638</t>
+          <t>562641</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1143116</t>
+          <t>1142916</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153057</t>
+          <t>1153056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10817</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661107</t>
+          <t>660965</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668167</t>
+          <t>668758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>654718</t>
+          <t>654461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1319666</t>
+          <t>1319593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1328565</t>
+          <t>1328540</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>10164</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>974</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15310</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635461</t>
+          <t>635884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>636729</t>
+          <t>638160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648101</t>
+          <t>648103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1279815</t>
+          <t>1280693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1293036</t>
+          <t>1293034</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>4064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16215</t>
+          <t>16132</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>6491</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19958</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>467862</t>
+          <t>468878</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476865</t>
+          <t>476851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>480634</t>
+          <t>480717</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>493197</t>
+          <t>492785</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>954809</t>
+          <t>954221</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>968436</t>
+          <t>968276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13198</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15301</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>328040</t>
+          <t>327963</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>364564</t>
+          <t>365429</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375540</t>
+          <t>375606</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>696459</t>
+          <t>696791</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>708975</t>
+          <t>708091</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7649</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18131</t>
+          <t>18397</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6128</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21742</t>
+          <t>20519</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>249349</t>
+          <t>250566</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>256191</t>
+          <t>256196</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>382038</t>
+          <t>381772</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396292</t>
+          <t>396256</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>635425</t>
+          <t>636648</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>651100</t>
+          <t>651039</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24787</t>
+          <t>25606</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>46915</t>
+          <t>48825</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>35217</t>
+          <t>37159</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>65188</t>
+          <t>67854</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3369563</t>
+          <t>3368744</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3386189</t>
+          <t>3385855</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3497627</t>
+          <t>3495717</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3520543</t>
+          <t>3520859</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6873704</t>
+          <t>6871038</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6903675</t>
+          <t>6901733</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1406-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1406-Edad-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>5715</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>8909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>449334</t>
+          <t>448431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>421085</t>
+          <t>421321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>874247</t>
+          <t>873410</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6482</t>
+          <t>6825</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680605</t>
+          <t>680262</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1290887</t>
+          <t>1291600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1966</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>12827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>675433</t>
+          <t>676218</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698430</t>
+          <t>697896</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707608</t>
+          <t>707606</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1378456</t>
+          <t>1378610</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1388510</t>
+          <t>1388554</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>8041</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23878</t>
+          <t>24008</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34561</t>
+          <t>35647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>590739</t>
+          <t>590609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>606428</t>
+          <t>606576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>597152</t>
+          <t>596278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>610176</t>
+          <t>610918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1194319</t>
+          <t>1193233</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1214980</t>
+          <t>1214387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18133</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25482</t>
+          <t>25758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>417834</t>
+          <t>417475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>427359</t>
+          <t>427339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>429667</t>
+          <t>428396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442470</t>
+          <t>442218</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>851747</t>
+          <t>851471</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>867761</t>
+          <t>868032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9548</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5155</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18324</t>
+          <t>18732</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>300238</t>
+          <t>299422</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>308696</t>
+          <t>308755</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>341871</t>
+          <t>340989</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>352024</t>
+          <t>351101</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>645458</t>
+          <t>645050</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>658564</t>
+          <t>658627</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19958</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>15094</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33585</t>
+          <t>34226</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229893</t>
+          <t>229967</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243569</t>
+          <t>243584</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>368448</t>
+          <t>368153</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382288</t>
+          <t>382118</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>604062</t>
+          <t>603421</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>622607</t>
+          <t>622553</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29682</t>
+          <t>28429</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54985</t>
+          <t>55170</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30711</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57239</t>
+          <t>57835</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>67000</t>
+          <t>65962</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104777</t>
+          <t>104166</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3371794</t>
+          <t>3371609</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3397097</t>
+          <t>3398350</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3496677</t>
+          <t>3496081</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3523205</t>
+          <t>3522545</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6875917</t>
+          <t>6876528</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6913694</t>
+          <t>6914732</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>388778</t>
+          <t>388692</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>808244</t>
+          <t>808237</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8403</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>984</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>583631</t>
+          <t>583622</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>555141</t>
+          <t>555997</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>562641</t>
+          <t>562648</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1142916</t>
+          <t>1143355</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1153056</t>
+          <t>1153050</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10890</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>660965</t>
+          <t>661044</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>668758</t>
+          <t>668175</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>654461</t>
+          <t>654880</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1319593</t>
+          <t>1318774</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1328540</t>
+          <t>1328552</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10164</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>975</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>11121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>16001</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635884</t>
+          <t>636109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>638160</t>
+          <t>637956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>648103</t>
+          <t>648102</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1280693</t>
+          <t>1279124</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1293034</t>
+          <t>1293019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9040</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4064</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16132</t>
+          <t>16179</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>20619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>468878</t>
+          <t>468924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>476851</t>
+          <t>476856</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>480717</t>
+          <t>480670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>492785</t>
+          <t>492720</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>954221</t>
+          <t>954148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>968276</t>
+          <t>968348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12333</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>16152</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>327963</t>
+          <t>327038</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>365429</t>
+          <t>365444</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>375606</t>
+          <t>375695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>696791</t>
+          <t>695940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>708091</t>
+          <t>708108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>805</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3913</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>18068</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6128</t>
+          <t>6037</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>22312</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250566</t>
+          <t>249798</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>256196</t>
+          <t>256193</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>381772</t>
+          <t>382101</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396256</t>
+          <t>396321</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>636648</t>
+          <t>634855</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>651039</t>
+          <t>651130</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25606</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23683</t>
+          <t>23505</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48825</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37159</t>
+          <t>36835</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>67854</t>
+          <t>66705</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3368744</t>
+          <t>3368726</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3385855</t>
+          <t>3385615</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3495717</t>
+          <t>3496666</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3520859</t>
+          <t>3521037</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6871038</t>
+          <t>6872187</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6901733</t>
+          <t>6902057</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
